--- a/templates/salary_form.xlsx
+++ b/templates/salary_form.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\salary_printer\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC-005\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98FB8D66-084A-47ED-946B-1B9F6617A6FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D3B3AF-D75B-4CC7-AC7D-4159429E89D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3525" yWindow="3000" windowWidth="23100" windowHeight="11295" tabRatio="597" xr2:uid="{7BA8934C-802B-44B9-8983-90AB6839C2C5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="597" xr2:uid="{7BA8934C-802B-44B9-8983-90AB6839C2C5}"/>
   </bookViews>
   <sheets>
     <sheet name="薪資單" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <t>勞保金額</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -50,10 +50,6 @@
   </si>
   <si>
     <t>應發薪資</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>月薪</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -163,6 +159,14 @@
   <si>
     <t>公司總計支出
 (A+C)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本薪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>職務加給</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -891,24 +895,6 @@
     <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -938,6 +924,24 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1273,11 +1277,11 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:5" s="2" customFormat="1" ht="27.75">
-      <c r="A2" s="50"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" ht="28.5" thickBot="1">
       <c r="A3" s="1"/>
@@ -1285,23 +1289,23 @@
     </row>
     <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="52"/>
+        <v>11</v>
+      </c>
+      <c r="B4" s="45"/>
+      <c r="C4" s="46"/>
       <c r="D4" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="25"/>
     </row>
     <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="A5" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
       <c r="D5" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" s="11"/>
     </row>
@@ -1312,68 +1316,68 @@
       <c r="B6" s="31"/>
       <c r="C6" s="31"/>
       <c r="D6" s="28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" s="29"/>
     </row>
     <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="54"/>
+        <v>30</v>
+      </c>
+      <c r="B7" s="47"/>
+      <c r="C7" s="48"/>
       <c r="D7" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7" s="20"/>
     </row>
     <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>7</v>
+      <c r="A8" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="B8" s="40"/>
       <c r="C8" s="40"/>
       <c r="D8" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8" s="21"/>
     </row>
     <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B9" s="40"/>
       <c r="C9" s="40"/>
       <c r="D9" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E9" s="21"/>
     </row>
     <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B10" s="40"/>
       <c r="C10" s="40"/>
       <c r="D10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E10" s="21"/>
     </row>
     <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B11" s="40"/>
       <c r="C11" s="40"/>
       <c r="D11" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E11" s="21"/>
     </row>
     <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B12" s="40"/>
       <c r="C12" s="40"/>
@@ -1384,7 +1388,7 @@
     </row>
     <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B13" s="40"/>
       <c r="C13" s="40"/>
@@ -1392,8 +1396,8 @@
       <c r="E13" s="22"/>
     </row>
     <row r="14" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="7" t="s">
-        <v>26</v>
+      <c r="A14" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="B14" s="40"/>
       <c r="C14" s="40"/>
@@ -1402,7 +1406,7 @@
     </row>
     <row r="15" spans="1:5" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="7" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B15" s="40"/>
       <c r="C15" s="40"/>
@@ -1410,7 +1414,9 @@
       <c r="E15" s="23"/>
     </row>
     <row r="16" spans="1:5" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A16" s="7"/>
+      <c r="A16" s="7" t="s">
+        <v>1</v>
+      </c>
       <c r="B16" s="43"/>
       <c r="C16" s="43"/>
       <c r="D16" s="4"/>
@@ -1418,88 +1424,88 @@
     </row>
     <row r="17" spans="1:5" ht="35.1" customHeight="1" thickBot="1">
       <c r="A17" s="14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" s="41"/>
       <c r="C17" s="42"/>
       <c r="D17" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E17" s="24"/>
     </row>
     <row r="18" spans="1:5" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A18" s="55" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="56"/>
-      <c r="C18" s="57"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="59"/>
+      <c r="A18" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="50"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="53"/>
     </row>
     <row r="19" spans="1:5" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="A19" s="30" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B19" s="31"/>
       <c r="C19" s="29"/>
       <c r="D19" s="30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19" s="29"/>
     </row>
-    <row r="20" spans="1:5" ht="39.950000000000003" customHeight="1">
+    <row r="20" spans="1:5" ht="55.5" customHeight="1">
       <c r="A20" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B20" s="34"/>
       <c r="C20" s="35"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="45"/>
-    </row>
-    <row r="21" spans="1:5" ht="39.950000000000003" customHeight="1">
-      <c r="A21" s="3" t="s">
-        <v>5</v>
+      <c r="D20" s="54"/>
+      <c r="E20" s="55"/>
+    </row>
+    <row r="21" spans="1:5" ht="55.5" customHeight="1">
+      <c r="A21" s="12" t="s">
+        <v>4</v>
       </c>
       <c r="B21" s="32"/>
       <c r="C21" s="33"/>
-      <c r="D21" s="46"/>
-      <c r="E21" s="47"/>
-    </row>
-    <row r="22" spans="1:5" ht="39.950000000000003" customHeight="1">
+      <c r="D21" s="56"/>
+      <c r="E21" s="57"/>
+    </row>
+    <row r="22" spans="1:5" ht="55.5" customHeight="1">
       <c r="A22" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B22" s="32"/>
       <c r="C22" s="33"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="47"/>
-    </row>
-    <row r="23" spans="1:5" ht="39.950000000000003" customHeight="1" thickBot="1">
+      <c r="D22" s="56"/>
+      <c r="E22" s="57"/>
+    </row>
+    <row r="23" spans="1:5" ht="55.5" customHeight="1" thickBot="1">
       <c r="A23" s="5" t="s">
         <v>1</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="37"/>
-      <c r="D23" s="46"/>
-      <c r="E23" s="47"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="57"/>
     </row>
     <row r="24" spans="1:5" ht="17.25" thickBot="1">
       <c r="A24" s="18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B24" s="38"/>
       <c r="C24" s="39"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="49"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="59"/>
     </row>
     <row r="25" spans="1:5" ht="54.95" customHeight="1" thickBot="1">
       <c r="A25" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B25" s="26"/>
       <c r="C25" s="27"/>
       <c r="D25" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E25" s="13"/>
     </row>
@@ -1534,7 +1540,7 @@
     <mergeCell ref="B8:C8"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:C5" xr:uid="{96D4A9BD-B9FD-483D-BF29-68DD26A43F60}">
       <formula1>#REF!</formula1>
     </dataValidation>
